--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-13T00:30:40+00:00</t>
+          <t>2026-09-14T00:33:12+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-14T00:33:12+00:00</t>
+          <t>2026-09-15T01:05:02+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-15T01:05:02+00:00</t>
+          <t>2026-09-16T00:54:15+00:00</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7">
@@ -566,7 +566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -600,12 +600,12 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>Blacklist (Call for Action)</t>
+          <t>Greylist (Increased Monitoring)</t>
         </is>
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>Democratic Republic of Korea</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="C2" s="7" t="inlineStr">
@@ -615,19 +615,19 @@
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>Blacklist (Call for Action)</t>
+          <t>Greylist (Increased Monitoring)</t>
         </is>
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
@@ -637,19 +637,19 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Blacklist (Call for Action)</t>
+          <t>Greylist (Increased Monitoring)</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Myanmar</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Cameroon</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Côte d'Ivoire</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Democratic Republic of the Congo</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Cameroon</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Côte d'Ivoire</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Democratic Republic of the Congo</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
@@ -825,7 +825,7 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Kuwait</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Lao PDR</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Lao PDR</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Papua New Guinea</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>South Sudan</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Papua New Guinea</t>
+          <t>Venezuela</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>South Sudan</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -1045,7 +1045,7 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Syria</t>
+          <t>Virgin Islands (UK)</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Venezuela</t>
+          <t>Yemen</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -1081,74 +1081,8 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>Vietnam</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t>19 June 2026</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>Virgin Islands (UK)</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>19 June 2026</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>Greylist (Increased Monitoring)</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>Yemen</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>19 June 2026</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:D26"/>
+  <autoFilter ref="A1:D23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$D$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-16T00:54:15+00:00</t>
+          <t>2026-09-17T02:23:18+00:00</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7">
@@ -566,7 +566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -600,12 +600,12 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>Greylist (Increased Monitoring)</t>
+          <t>Blacklist (Call for Action)</t>
         </is>
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>Democratic Republic of Korea</t>
         </is>
       </c>
       <c r="C2" s="7" t="inlineStr">
@@ -615,19 +615,19 @@
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>Greylist (Increased Monitoring)</t>
+          <t>Blacklist (Call for Action)</t>
         </is>
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
@@ -637,19 +637,19 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Greylist (Increased Monitoring)</t>
+          <t>Blacklist (Call for Action)</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Myanmar</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Cameroon</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Côte d'Ivoire</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Democratic Republic of the Congo</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Cameroon</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Côte d'Ivoire</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Democratic Republic of the Congo</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
@@ -825,7 +825,7 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Lao PDR</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Kuwait</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Lao PDR</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Papua New Guinea</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>South Sudan</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Syria</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Venezuela</t>
+          <t>Papua New Guinea</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>South Sudan</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -1045,7 +1045,7 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Virgin Islands (UK)</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -1067,22 +1067,88 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>19 June 2026</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>19 June 2026</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Virgin Islands (UK)</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>19 June 2026</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>Greylist (Increased Monitoring)</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
           <t>Yemen</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>19 June 2026</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>19 June 2026</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
         <is>
           <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D23"/>
+  <autoFilter ref="A1:D26"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-17T02:23:18+00:00</t>
+          <t>2026-09-18T00:54:33+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-18T00:54:33+00:00</t>
+          <t>2026-09-20T00:31:20+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-20T00:31:20+00:00</t>
+          <t>2026-09-23T01:04:34+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions.html</t>
+          <t>https://fiaumalta.org/country-statements/</t>
         </is>
       </c>
     </row>
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-23T01:04:34+00:00</t>
+          <t>2026-10-24T15:22:34+00:00</t>
         </is>
       </c>
     </row>
@@ -528,24 +528,36 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Fetch strategy</t>
+          <t>Source provider</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>playwright</t>
+          <t>FIAU 转载 FATF</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
+          <t>Fetch strategy</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>fiau-pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
           <t>Extraction</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>country-facet</t>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>fiau-pdf-active-list</t>
         </is>
       </c>
     </row>
@@ -605,17 +617,17 @@
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>Democratic Republic of Korea</t>
+          <t>Democratic People's Republic of Korea</t>
         </is>
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
-          <t>19 June 2026</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
+          <t>https://fiaumalta.org/app/uploads/2026/06/FATF-Public-Statement-19-June-2026-High-risk.pdf</t>
         </is>
       </c>
     </row>
@@ -632,12 +644,12 @@
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>19 June 2026</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
+          <t>https://fiaumalta.org/app/uploads/2026/06/FATF-Public-Statement-19-June-2026-High-risk.pdf</t>
         </is>
       </c>
     </row>
@@ -654,12 +666,12 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>19 June 2026</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/call-for-action-june-2026.html</t>
+          <t>https://fiaumalta.org/app/uploads/2026/06/FATF-Public-Statement-19-June-2026-High-risk.pdf</t>
         </is>
       </c>
     </row>
@@ -671,17 +683,17 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>ANGOLA</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>19 June 2026</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://fiaumalta.org/app/uploads/2026/06/FATF-On-going-Process-19-June-2026-Increased-monitoring.pdf</t>
         </is>
       </c>
     </row>
@@ -693,17 +705,17 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>BOLIVIA</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>19 June 2026</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://fiaumalta.org/app/uploads/2026/06/FATF-On-going-Process-19-June-2026-Increased-monitoring.pdf</t>
         </is>
       </c>
     </row>
@@ -715,17 +727,17 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>BOSNIA AND HERZEGOVINA</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>19 June 2026</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://fiaumalta.org/app/uploads/2026/06/FATF-On-going-Process-19-June-2026-Increased-monitoring.pdf</t>
         </is>
       </c>
     </row>
@@ -737,17 +749,17 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>BULGARIA</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>19 June 2026</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://fiaumalta.org/app/uploads/2026/06/FATF-On-going-Process-19-June-2026-Increased-monitoring.pdf</t>
         </is>
       </c>
     </row>
@@ -759,17 +771,17 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Cameroon</t>
+          <t>CAMEROON</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>19 June 2026</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://fiaumalta.org/app/uploads/2026/06/FATF-On-going-Process-19-June-2026-Increased-monitoring.pdf</t>
         </is>
       </c>
     </row>
@@ -781,17 +793,17 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Côte d'Ivoire</t>
+          <t>CÔTE D’IVOIRE</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>19 June 2026</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://fiaumalta.org/app/uploads/2026/06/FATF-On-going-Process-19-June-2026-Increased-monitoring.pdf</t>
         </is>
       </c>
     </row>
@@ -803,17 +815,17 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Democratic Republic of the Congo</t>
+          <t>DEMOCRATIC REPUBLIC OF THE CONGO</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>19 June 2026</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://fiaumalta.org/app/uploads/2026/06/FATF-On-going-Process-19-June-2026-Increased-monitoring.pdf</t>
         </is>
       </c>
     </row>
@@ -825,17 +837,17 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>HAITI</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>19 June 2026</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://fiaumalta.org/app/uploads/2026/06/FATF-On-going-Process-19-June-2026-Increased-monitoring.pdf</t>
         </is>
       </c>
     </row>
@@ -847,17 +859,17 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>IRAQ</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>19 June 2026</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://fiaumalta.org/app/uploads/2026/06/FATF-On-going-Process-19-June-2026-Increased-monitoring.pdf</t>
         </is>
       </c>
     </row>
@@ -869,17 +881,17 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>KENYA</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>19 June 2026</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://fiaumalta.org/app/uploads/2026/06/FATF-On-going-Process-19-June-2026-Increased-monitoring.pdf</t>
         </is>
       </c>
     </row>
@@ -891,17 +903,17 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>KUWAIT</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>19 June 2026</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://fiaumalta.org/app/uploads/2026/06/FATF-On-going-Process-19-June-2026-Increased-monitoring.pdf</t>
         </is>
       </c>
     </row>
@@ -913,17 +925,17 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Lao PDR</t>
+          <t>LAO PDR</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>19 June 2026</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://fiaumalta.org/app/uploads/2026/06/FATF-On-going-Process-19-June-2026-Increased-monitoring.pdf</t>
         </is>
       </c>
     </row>
@@ -935,17 +947,17 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>LEBANON</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>19 June 2026</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://fiaumalta.org/app/uploads/2026/06/FATF-On-going-Process-19-June-2026-Increased-monitoring.pdf</t>
         </is>
       </c>
     </row>
@@ -957,17 +969,17 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>MONACO</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>19 June 2026</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://fiaumalta.org/app/uploads/2026/06/FATF-On-going-Process-19-June-2026-Increased-monitoring.pdf</t>
         </is>
       </c>
     </row>
@@ -979,17 +991,17 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>NEPAL</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>19 June 2026</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://fiaumalta.org/app/uploads/2026/06/FATF-On-going-Process-19-June-2026-Increased-monitoring.pdf</t>
         </is>
       </c>
     </row>
@@ -1006,12 +1018,12 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>19 June 2026</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://fiaumalta.org/app/uploads/2026/06/FATF-On-going-Process-19-June-2026-Increased-monitoring.pdf</t>
         </is>
       </c>
     </row>
@@ -1023,17 +1035,17 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>South Sudan</t>
+          <t>SOUTH SUDAN</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>19 June 2026</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://fiaumalta.org/app/uploads/2026/06/FATF-On-going-Process-19-June-2026-Increased-monitoring.pdf</t>
         </is>
       </c>
     </row>
@@ -1045,17 +1057,17 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Syria</t>
+          <t>SYRIA</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>19 June 2026</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://fiaumalta.org/app/uploads/2026/06/FATF-On-going-Process-19-June-2026-Increased-monitoring.pdf</t>
         </is>
       </c>
     </row>
@@ -1067,17 +1079,17 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Venezuela</t>
+          <t>VENEZUELA</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>19 June 2026</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://fiaumalta.org/app/uploads/2026/06/FATF-On-going-Process-19-June-2026-Increased-monitoring.pdf</t>
         </is>
       </c>
     </row>
@@ -1089,17 +1101,17 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>VIETNAM</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>19 June 2026</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://fiaumalta.org/app/uploads/2026/06/FATF-On-going-Process-19-June-2026-Increased-monitoring.pdf</t>
         </is>
       </c>
     </row>
@@ -1111,17 +1123,17 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Virgin Islands (UK)</t>
+          <t>VIRGIN ISLANDS (UK)</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>19 June 2026</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://fiaumalta.org/app/uploads/2026/06/FATF-On-going-Process-19-June-2026-Increased-monitoring.pdf</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1145,17 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Yemen</t>
+          <t>YEMEN</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>19 June 2026</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
+          <t>https://fiaumalta.org/app/uploads/2026/06/FATF-On-going-Process-19-June-2026-Increased-monitoring.pdf</t>
         </is>
       </c>
     </row>

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-24T15:22:34+00:00</t>
+          <t>2026-10-24T17:44:12+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-24T17:44:12+00:00</t>
+          <t>2026-10-24T21:20:30+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-24T21:20:30+00:00</t>
+          <t>2026-10-25T00:42:21+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-25T00:42:21+00:00</t>
+          <t>2026-10-25T07:57:08+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-25T07:57:08+00:00</t>
+          <t>2026-10-25T14:42:37+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-25T14:42:37+00:00</t>
+          <t>2026-10-25T18:00:17+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-25T18:00:17+00:00</t>
+          <t>2026-10-25T21:25:19+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-25T21:25:19+00:00</t>
+          <t>2026-10-26T00:56:41+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-26T00:56:41+00:00</t>
+          <t>2026-10-26T08:28:21+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-26T08:28:21+00:00</t>
+          <t>2026-10-26T17:04:41+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-26T17:04:41+00:00</t>
+          <t>2026-10-26T22:56:59+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-26T22:56:59+00:00</t>
+          <t>2026-10-27T01:44:31+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-27T01:44:31+00:00</t>
+          <t>2026-10-27T01:47:42+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-27T01:47:42+00:00</t>
+          <t>2026-10-27T08:31:36+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-27T08:31:36+00:00</t>
+          <t>2026-10-27T16:07:57+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-27T16:07:57+00:00</t>
+          <t>2026-10-27T22:46:29+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-27T22:46:29+00:00</t>
+          <t>2026-10-28T01:55:56+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-28T01:55:56+00:00</t>
+          <t>2026-10-28T09:09:43+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-28T09:09:43+00:00</t>
+          <t>2026-10-28T16:55:18+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-28T16:55:18+00:00</t>
+          <t>2026-10-28T22:55:21+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-28T22:55:21+00:00</t>
+          <t>2026-10-29T02:00:29+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-29T02:00:29+00:00</t>
+          <t>2026-10-29T06:40:49+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-29T06:40:49+00:00</t>
+          <t>2026-10-29T09:09:09+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-29T09:09:09+00:00</t>
+          <t>2026-10-29T17:13:02+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-29T17:13:02+00:00</t>
+          <t>2026-10-29T23:03:28+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-29T23:03:28+00:00</t>
+          <t>2026-10-30T02:16:46+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-30T02:16:46+00:00</t>
+          <t>2026-10-30T09:20:01+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-30T09:20:01+00:00</t>
+          <t>2026-10-30T16:54:03+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-30T16:54:03+00:00</t>
+          <t>2026-10-30T22:44:34+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/fatf-jurisdictions.xlsx
+++ b/public/downloads/fatf-jurisdictions.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-30T22:44:34+00:00</t>
+          <t>2026-10-31T01:56:00+00:00</t>
         </is>
       </c>
     </row>
